--- a/bi/tkDashboard/管理模块/视频数据/doc/视频标签判定规则_给IT_6.xlsx
+++ b/bi/tkDashboard/管理模块/视频数据/doc/视频标签判定规则_给IT_6.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13160"/>
+    <workbookView windowHeight="23960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="视频标签表-实际结构" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="133">
   <si>
     <t>基础信息</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>仅对"自制视频"大类适用；与"是否AI视频"是同一个判断条件的两面，二者永远相反(不会同时为"是")</t>
+  </si>
+  <si>
+    <t>☑️</t>
   </si>
   <si>
     <t>图文在"照片详情"，判别自制的方法与视频一致，都是匹配Post ID或Username</t>
@@ -2147,13 +2150,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="25.9615384615385" customWidth="1"/>
+    <col min="4" max="4" width="38.4807692307692" customWidth="1"/>
     <col min="5" max="5" width="101.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2429,7 +2432,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:5">
+    <row r="17" ht="30" customHeight="1" spans="1:7">
       <c r="A17" s="3" t="s">
         <v>112</v>
       </c>
@@ -2445,8 +2448,11 @@
       <c r="E17" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:5">
+      <c r="G17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:7">
       <c r="A18" s="3" t="s">
         <v>112</v>
       </c>
@@ -2454,16 +2460,16 @@
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="1:5">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:7">
       <c r="A19" s="3" t="s">
         <v>112</v>
       </c>
@@ -2471,16 +2477,19 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="1:5">
+        <v>119</v>
+      </c>
+      <c r="G19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:7">
       <c r="A20" s="3" t="s">
         <v>112</v>
       </c>
@@ -2488,16 +2497,19 @@
         <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" spans="1:5">
+        <v>121</v>
+      </c>
+      <c r="G20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:7">
       <c r="A21" s="3" t="s">
         <v>112</v>
       </c>
@@ -2505,13 +2517,16 @@
         <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="G21" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2533,13 +2548,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:3">
@@ -2547,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="4">
         <v>3</v>
@@ -2558,7 +2573,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" s="4">
         <v>2</v>
@@ -2569,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4">
         <v>4</v>
@@ -2580,7 +2595,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C5" s="4">
         <v>4</v>
@@ -2591,7 +2606,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
@@ -2602,7 +2617,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
@@ -2613,7 +2628,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4">
         <v>2</v>
@@ -2624,7 +2639,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" s="4">
         <v>2</v>
@@ -2635,7 +2650,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="4">
         <v>2</v>
@@ -2646,7 +2661,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4">
         <v>2</v>
@@ -2654,7 +2669,7 @@
     </row>
     <row r="13" ht="409" customHeight="1" spans="1:3">
       <c r="A13" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
